--- a/outputs/58032.xlsx
+++ b/outputs/58032.xlsx
@@ -131,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,13 +167,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -243,32 +236,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -527,772 +524,849 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B2)*($J$2:$J$32=$C2),0),0))</f>
+      <c r="A2" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B2)*($J$3:$J$32=$C2),0),0))</f>
         <v>Arthur Strout</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>307490</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="4"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B3)*($J$2:$J$32=$C3),0),0))</f>
+      <c r="A3" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B3)*($J$3:$J$32=$C3),0),0))</f>
         <v>Tyler Morrison</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>342441</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="4"/>
-      <c r="H3" s="6" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="6" t="n">
+      <c r="I3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="7" t="n">
         <v>306228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B4)*($J$2:$J$32=$C4),0),0))</f>
+      <c r="A4" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B4)*($J$3:$J$32=$C4),0),0))</f>
         <v>Mario Morales</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>345321</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="4"/>
-      <c r="H4" s="6" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>331186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B5)*($J$2:$J$32=$C5),0),0))</f>
+      <c r="A5" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B5)*($J$3:$J$32=$C5),0),0))</f>
         <v>Hillary Rooslet</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>331383</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="4"/>
-      <c r="H5" s="6" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="7" t="n">
         <v>354028</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B6)*($J$2:$J$32=$C6),0),0))</f>
+      <c r="A6" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B6)*($J$3:$J$32=$C6),0),0))</f>
         <v>Natasha Kilebrew</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>336421</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="4"/>
-      <c r="H6" s="6" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="I6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="n">
         <v>303465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B7)*($J$2:$J$32=$C7),0),0))</f>
+      <c r="A7" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B7)*($J$3:$J$32=$C7),0),0))</f>
         <v>Sidneia Moraes</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>351927</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4"/>
-      <c r="H7" s="6" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="I7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="7" t="n">
         <v>330462</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B8)*($J$2:$J$32=$C8),0),0))</f>
+      <c r="A8" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B8)*($J$3:$J$32=$C8),0),0))</f>
         <v>Corey Martin</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>338416</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="4"/>
-      <c r="H8" s="6" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="I8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="7" t="n">
         <v>336668</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B9)*($J$2:$J$32=$C9),0),0))</f>
+      <c r="A9" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B9)*($J$3:$J$32=$C9),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>338424</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="4"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B10)*($J$2:$J$32=$C10),0),0))</f>
+      <c r="A10" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B10)*($J$3:$J$32=$C10),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>349843</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="4"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B11)*($J$2:$J$32=$C11),0),0))</f>
+      <c r="A11" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B11)*($J$3:$J$32=$C11),0),0))</f>
         <v>Nicole Peterson</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>356946</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="4"/>
-      <c r="H11" s="6" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" s="6" t="n">
+      <c r="I11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="7" t="n">
         <v>357114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B12)*($J$2:$J$32=$C12),0),0))</f>
+      <c r="A12" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B12)*($J$3:$J$32=$C12),0),0))</f>
         <v>Magda Da Silva</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>338120</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="4"/>
-      <c r="H12" s="6" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="6" t="n">
+      <c r="I12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="7" t="n">
         <v>307490</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B13)*($J$2:$J$32=$C13),0),0))</f>
+      <c r="A13" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B13)*($J$3:$J$32=$C13),0),0))</f>
         <v>Jose Alicea</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>303453</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="4"/>
-      <c r="H13" s="6" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J13" s="6" t="n">
+      <c r="I13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="7" t="n">
         <v>331383</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B14)*($J$2:$J$32=$C14),0),0))</f>
+      <c r="A14" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B14)*($J$3:$J$32=$C14),0),0))</f>
         <v>Dayana Papi</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>331381</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
-      <c r="H14" s="6" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="6" t="n">
+      <c r="I14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>336421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B15)*($J$2:$J$32=$C15),0),0))</f>
+      <c r="A15" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B15)*($J$3:$J$32=$C15),0),0))</f>
         <v>Andrew Ballard</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="n">
+      <c r="B15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="n">
         <v>348873</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-      <c r="H15" s="6" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="6" t="n">
+      <c r="I15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="7" t="n">
         <v>342441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B16)*($J$2:$J$32=$C16),0),0))</f>
+      <c r="A16" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B16)*($J$3:$J$32=$C16),0),0))</f>
         <v>Alexander Urias</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="4" t="n">
+      <c r="B16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="n">
         <v>351596</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
-      <c r="H16" s="6" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" s="6" t="n">
+      <c r="I16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="7" t="n">
         <v>345321</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B17)*($J$2:$J$32=$C17),0),0))</f>
+      <c r="A17" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B17)*($J$3:$J$32=$C17),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>343348</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
-      <c r="H17" s="6" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="6" t="n">
+      <c r="I17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="7" t="n">
         <v>338120</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B18)*($J$2:$J$32=$C18),0),0))</f>
+      <c r="A18" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B18)*($J$3:$J$32=$C18),0),0))</f>
         <v>Diane Valentin</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="4" t="n">
+      <c r="B18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>338123</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
-      <c r="H18" s="6" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="6" t="n">
+      <c r="I18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="7" t="n">
         <v>338416</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B19)*($J$2:$J$32=$C19),0),0))</f>
+      <c r="A19" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B19)*($J$3:$J$32=$C19),0),0))</f>
         <v>Kamela Abrantes</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="4" t="n">
+      <c r="B19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>303462</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
-      <c r="H19" s="6" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J19" s="6" t="n">
+      <c r="I19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="7" t="n">
         <v>351927</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B20)*($J$2:$J$32=$C20),0),0))</f>
+      <c r="A20" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B20)*($J$3:$J$32=$C20),0),0))</f>
         <v>Jennifer Challet</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="4" t="n">
+      <c r="B20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>339861</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
-      <c r="H20" s="6" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="6" t="n">
+      <c r="I20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="7" t="n">
         <v>356946</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B21)*($J$2:$J$32=$C21),0),0))</f>
+      <c r="A21" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B21)*($J$3:$J$32=$C21),0),0))</f>
         <v>ARTJOLA BARDHOSHI</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="4" t="n">
+      <c r="B21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="5" t="n">
         <v>336667</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
-      <c r="H21" s="6" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="6" t="n">
+      <c r="I21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="7" t="n">
         <v>303462</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B22)*($J$2:$J$32=$C22),0),0))</f>
+      <c r="A22" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B22)*($J$3:$J$32=$C22),0),0))</f>
         <v>Wayne Fisher</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="B22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5" t="n">
         <v>336668</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
-      <c r="H22" s="6" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>303462</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B23)*($J$2:$J$32=$C23),0),0))</f>
+      <c r="A23" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B23)*($J$3:$J$32=$C23),0),0))</f>
         <v>Matthew Wusteney</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="4" t="n">
+      <c r="B23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5" t="n">
         <v>306228</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="H23" s="6" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="6" t="n">
+      <c r="I23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="7" t="n">
         <v>336667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B24)*($J$2:$J$32=$C24),0),0))</f>
+      <c r="A24" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B24)*($J$3:$J$32=$C24),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="5" t="n">
         <v>331185</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B25)*($J$2:$J$32=$C25),0),0))</f>
+      <c r="A25" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B25)*($J$3:$J$32=$C25),0),0))</f>
         <v>Eliane Webb</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="4" t="n">
+      <c r="B25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="5" t="n">
         <v>331186</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
-      <c r="H25" s="6" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" s="6" t="n">
+      <c r="I25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="7" t="n">
         <v>338123</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B26)*($J$2:$J$32=$C26),0),0))</f>
+      <c r="A26" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B26)*($J$3:$J$32=$C26),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="5" t="n">
         <v>352767</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
-      <c r="H26" s="6" t="s">
+      <c r="D26" s="6"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="6" t="n">
+      <c r="I26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="7" t="n">
         <v>339861</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B27)*($J$2:$J$32=$C27),0),0))</f>
+      <c r="A27" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B27)*($J$3:$J$32=$C27),0),0))</f>
         <v>Lora-lee Ciallella</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5" t="n">
         <v>354028</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
-      <c r="H27" s="6" t="s">
+      <c r="D27" s="6"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="6" t="n">
+      <c r="I27" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="7" t="n">
         <v>337678</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B28)*($J$2:$J$32=$C28),0),0))</f>
+      <c r="A28" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B28)*($J$3:$J$32=$C28),0),0))</f>
         <v>John Rice</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="4" t="n">
+      <c r="B28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5" t="n">
         <v>303465</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
-      <c r="H28" s="6" t="s">
+      <c r="D28" s="6"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J28" s="6" t="n">
+      <c r="I28" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J28" s="7" t="n">
         <v>343363</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B29)*($J$2:$J$32=$C29),0),0))</f>
+      <c r="A29" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B29)*($J$3:$J$32=$C29),0),0))</f>
         <v>Fabiana Santos</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="4" t="n">
+      <c r="B29" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="5" t="n">
         <v>357114</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
-      <c r="H29" s="6" t="s">
+      <c r="D29" s="6"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="6" t="n">
+      <c r="I29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="7" t="n">
         <v>303453</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B30)*($J$2:$J$32=$C30),0),0))</f>
+      <c r="A30" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B30)*($J$3:$J$32=$C30),0),0))</f>
         <v>Dina Simoes</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="4" t="n">
+      <c r="B30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="5" t="n">
         <v>330462</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
-      <c r="H30" s="6" t="s">
+      <c r="D30" s="6"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30" s="6" t="n">
+      <c r="I30" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="7" t="n">
         <v>331381</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B31)*($J$2:$J$32=$C31),0),0))</f>
+      <c r="A31" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B31)*($J$3:$J$32=$C31),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="4" t="n">
+      <c r="B31" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5" t="n">
         <v>337680</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="H31" s="6" t="s">
+      <c r="D31" s="6"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J31" s="6" t="n">
+      <c r="I31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="7" t="n">
         <v>348873</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B32)*($J$2:$J$32=$C32),0),0))</f>
+      <c r="A32" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B32)*($J$3:$J$32=$C32),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="4" t="n">
+      <c r="B32" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5" t="n">
         <v>310018</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
-      <c r="H32" s="6" t="s">
+      <c r="D32" s="6"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="6" t="n">
+      <c r="I32" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="7" t="n">
         <v>351596</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B33)*($J$2:$J$32=$C33),0),0))</f>
+      <c r="A33" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B33)*($J$3:$J$32=$C33),0),0))</f>
         <v>Stephanie Rasun</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="4" t="n">
+      <c r="B33" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="5" t="n">
         <v>337678</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="str">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B34)*($J$2:$J$32=$C34),0),0))</f>
+      <c r="A34" s="4" t="str">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B34)*($J$3:$J$32=$C34),0),0))</f>
         <v>Kristen Ennis</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="4" t="n">
+      <c r="B34" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="5" t="n">
         <v>343363</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="e">
-        <f aca="false">INDEX($H$2:$H$32,MATCH(1,INDEX(($I$2:$I$32=$B35)*($J$2:$J$32=$C35),0),0))</f>
+      <c r="A35" s="4" t="e">
+        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B35)*($J$3:$J$32=$C35),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="B35" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="n">
         <v>340437</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="4"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/58032.xlsx
+++ b/outputs/58032.xlsx
@@ -236,7 +236,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -249,7 +249,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -263,6 +263,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -562,7 +566,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B2)*($J$3:$J$32=$C2),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B2)*($J$2:$J$35=$C2),0)),"")</f>
         <v>Arthur Strout</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -573,15 +577,15 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B3)*($J$3:$J$32=$C3),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B3)*($J$2:$J$35=$C3),0)),"")</f>
         <v>Tyler Morrison</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -592,21 +596,21 @@
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="7" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="7" t="n">
+      <c r="I3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="8" t="n">
         <v>306228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B4)*($J$3:$J$32=$C4),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B4)*($J$2:$J$35=$C4),0)),"")</f>
         <v>Mario Morales</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -617,21 +621,21 @@
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="7" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="7" t="n">
+      <c r="I4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="8" t="n">
         <v>331186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B5)*($J$3:$J$32=$C5),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B5)*($J$2:$J$35=$C5),0)),"")</f>
         <v>Hillary Rooslet</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -642,21 +646,21 @@
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="7" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="7" t="n">
+      <c r="I5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="8" t="n">
         <v>354028</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B6)*($J$3:$J$32=$C6),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B6)*($J$2:$J$35=$C6),0)),"")</f>
         <v>Natasha Kilebrew</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -667,21 +671,21 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="7" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="n">
+      <c r="I6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="8" t="n">
         <v>303465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B7)*($J$3:$J$32=$C7),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B7)*($J$2:$J$35=$C7),0)),"")</f>
         <v>Sidneia Moraes</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -692,21 +696,21 @@
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="7" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" s="7" t="n">
+      <c r="I7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="8" t="n">
         <v>330462</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B8)*($J$3:$J$32=$C8),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B8)*($J$2:$J$35=$C8),0)),"")</f>
         <v>Corey Martin</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -717,22 +721,22 @@
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="7" t="s">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="7" t="n">
+      <c r="I8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="8" t="n">
         <v>336668</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B9)*($J$3:$J$32=$C9),0),0))</f>
-        <v>#N/A</v>
+      <c r="A9" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B9)*($J$2:$J$35=$C9),0)),"")</f>
+        <v/>
       </c>
       <c r="B9" s="5" t="s">
         <v>5</v>
@@ -742,16 +746,16 @@
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B10)*($J$3:$J$32=$C10),0),0))</f>
-        <v>#N/A</v>
+      <c r="A10" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B10)*($J$2:$J$35=$C10),0)),"")</f>
+        <v/>
       </c>
       <c r="B10" s="5" t="s">
         <v>5</v>
@@ -761,15 +765,15 @@
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B11)*($J$3:$J$32=$C11),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B11)*($J$2:$J$35=$C11),0)),"")</f>
         <v>Nicole Peterson</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -780,21 +784,21 @@
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="7" t="s">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" s="7" t="n">
+      <c r="I11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="8" t="n">
         <v>357114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B12)*($J$3:$J$32=$C12),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B12)*($J$2:$J$35=$C12),0)),"")</f>
         <v>Magda Da Silva</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -805,21 +809,21 @@
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="7" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="7" t="n">
+      <c r="I12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="8" t="n">
         <v>307490</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B13)*($J$3:$J$32=$C13),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B13)*($J$2:$J$35=$C13),0)),"")</f>
         <v>Jose Alicea</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -830,21 +834,21 @@
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="7" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J13" s="7" t="n">
+      <c r="I13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>331383</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B14)*($J$3:$J$32=$C14),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B14)*($J$2:$J$35=$C14),0)),"")</f>
         <v>Dayana Papi</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -855,21 +859,21 @@
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="7" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="7" t="n">
+      <c r="I14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="8" t="n">
         <v>336421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B15)*($J$3:$J$32=$C15),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B15)*($J$2:$J$35=$C15),0)),"")</f>
         <v>Andrew Ballard</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -880,21 +884,21 @@
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="7" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="7" t="n">
+      <c r="I15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>342441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B16)*($J$3:$J$32=$C16),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B16)*($J$2:$J$35=$C16),0)),"")</f>
         <v>Alexander Urias</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -905,22 +909,22 @@
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="7" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" s="7" t="n">
+      <c r="I16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="8" t="n">
         <v>345321</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B17)*($J$3:$J$32=$C17),0),0))</f>
-        <v>#N/A</v>
+      <c r="A17" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B17)*($J$2:$J$35=$C17),0)),"")</f>
+        <v/>
       </c>
       <c r="B17" s="5" t="s">
         <v>5</v>
@@ -930,21 +934,21 @@
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="7" t="s">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="7" t="n">
+      <c r="I17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="8" t="n">
         <v>338120</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B18)*($J$3:$J$32=$C18),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B18)*($J$2:$J$35=$C18),0)),"")</f>
         <v>Diane Valentin</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -955,21 +959,21 @@
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="7" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="7" t="n">
+      <c r="I18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="8" t="n">
         <v>338416</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B19)*($J$3:$J$32=$C19),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B19)*($J$2:$J$35=$C19),0)),"")</f>
         <v>Kamela Abrantes</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -980,21 +984,21 @@
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="7" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J19" s="7" t="n">
+      <c r="I19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="8" t="n">
         <v>351927</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B20)*($J$3:$J$32=$C20),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B20)*($J$2:$J$35=$C20),0)),"")</f>
         <v>Jennifer Challet</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -1005,21 +1009,21 @@
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="7" t="s">
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="7" t="n">
+      <c r="I20" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="8" t="n">
         <v>356946</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B21)*($J$3:$J$32=$C21),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B21)*($J$2:$J$35=$C21),0)),"")</f>
         <v>ARTJOLA BARDHOSHI</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1030,21 +1034,21 @@
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="7" t="s">
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="7" t="n">
+      <c r="I21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="8" t="n">
         <v>303462</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B22)*($J$3:$J$32=$C22),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B22)*($J$2:$J$35=$C22),0)),"")</f>
         <v>Wayne Fisher</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -1055,21 +1059,21 @@
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="7" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="8" t="n">
         <v>303462</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B23)*($J$3:$J$32=$C23),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B23)*($J$2:$J$35=$C23),0)),"")</f>
         <v>Matthew Wusteney</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1080,22 +1084,22 @@
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="7" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="7" t="n">
+      <c r="I23" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="8" t="n">
         <v>336667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B24)*($J$3:$J$32=$C24),0),0))</f>
-        <v>#N/A</v>
+      <c r="A24" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B24)*($J$2:$J$35=$C24),0)),"")</f>
+        <v/>
       </c>
       <c r="B24" s="5" t="s">
         <v>5</v>
@@ -1105,15 +1109,15 @@
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B25)*($J$3:$J$32=$C25),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B25)*($J$2:$J$35=$C25),0)),"")</f>
         <v>Eliane Webb</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1124,22 +1128,22 @@
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="7" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" s="7" t="n">
+      <c r="I25" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="8" t="n">
         <v>338123</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B26)*($J$3:$J$32=$C26),0),0))</f>
-        <v>#N/A</v>
+      <c r="A26" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B26)*($J$2:$J$35=$C26),0)),"")</f>
+        <v/>
       </c>
       <c r="B26" s="5" t="s">
         <v>5</v>
@@ -1149,21 +1153,21 @@
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="7" t="s">
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="7" t="n">
+      <c r="I26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="8" t="n">
         <v>339861</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B27)*($J$3:$J$32=$C27),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B27)*($J$2:$J$35=$C27),0)),"")</f>
         <v>Lora-lee Ciallella</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1174,21 +1178,21 @@
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="7" t="s">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="7" t="n">
+      <c r="I27" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="8" t="n">
         <v>337678</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B28)*($J$3:$J$32=$C28),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B28)*($J$2:$J$35=$C28),0)),"")</f>
         <v>John Rice</v>
       </c>
       <c r="B28" s="5" t="s">
@@ -1199,21 +1203,21 @@
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="7" t="s">
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J28" s="7" t="n">
+      <c r="I28" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J28" s="8" t="n">
         <v>343363</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B29)*($J$3:$J$32=$C29),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B29)*($J$2:$J$35=$C29),0)),"")</f>
         <v>Fabiana Santos</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1224,21 +1228,21 @@
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="7" t="s">
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="7" t="n">
+      <c r="I29" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="8" t="n">
         <v>303453</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B30)*($J$3:$J$32=$C30),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B30)*($J$2:$J$35=$C30),0)),"")</f>
         <v>Dina Simoes</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -1249,22 +1253,22 @@
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="7" t="s">
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30" s="7" t="n">
+      <c r="I30" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="8" t="n">
         <v>331381</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B31)*($J$3:$J$32=$C31),0),0))</f>
-        <v>#N/A</v>
+      <c r="A31" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B31)*($J$2:$J$35=$C31),0)),"")</f>
+        <v/>
       </c>
       <c r="B31" s="5" t="s">
         <v>5</v>
@@ -1274,22 +1278,22 @@
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="7" t="s">
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J31" s="7" t="n">
+      <c r="I31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="8" t="n">
         <v>348873</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B32)*($J$3:$J$32=$C32),0),0))</f>
-        <v>#N/A</v>
+      <c r="A32" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B32)*($J$2:$J$35=$C32),0)),"")</f>
+        <v/>
       </c>
       <c r="B32" s="5" t="s">
         <v>5</v>
@@ -1299,21 +1303,21 @@
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="7" t="s">
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="7" t="n">
+      <c r="I32" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="8" t="n">
         <v>351596</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B33)*($J$3:$J$32=$C33),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B33)*($J$2:$J$35=$C33),0)),"")</f>
         <v>Stephanie Rasun</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1324,15 +1328,15 @@
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="str">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B34)*($J$3:$J$32=$C34),0),0))</f>
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B34)*($J$2:$J$35=$C34),0)),"")</f>
         <v>Kristen Ennis</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -1343,16 +1347,16 @@
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="e">
-        <f aca="false">INDEX($H$3:$H$32,MATCH(1,INDEX(($I$3:$I$32=$B35)*($J$3:$J$32=$C35),0),0))</f>
-        <v>#N/A</v>
+      <c r="A35" s="4" t="str">
+        <f aca="false">IFERROR(INDEX($H$2:$H$35,MATCH(1,($I$2:$I$35=$B35)*($J$2:$J$35=$C35),0)),"")</f>
+        <v/>
       </c>
       <c r="B35" s="5" t="s">
         <v>5</v>
@@ -1362,11 +1366,11 @@
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
